--- a/Praktikum 1_ Metode Numerik - Pencarian Akar.xlsx
+++ b/Praktikum 1_ Metode Numerik - Pencarian Akar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Maria\Github\Metode-Numerik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C89F6476-F421-49E8-B8F3-F4ED05F91916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D063113-E39A-41B0-8BB7-F46D03BADF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{94FCD8C2-7E8B-4EF5-86D5-EE480A84D8B6}"/>
   </bookViews>
@@ -304,9 +304,13 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -319,25 +323,21 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1778,6 +1778,450 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID"/>
+              <a:t>metode Secant</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AU$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>x_n</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AU$5:$AU$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.0000">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>1.7272727272727273</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>1.7321428571428572</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>1.7320506804317222</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0ABA-45DA-9564-EE1511FF81C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="824978944"/>
+        <c:axId val="775216464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="824978944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Iterasi</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="775216464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="775216464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>x</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="824978944"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
@@ -1864,6 +2308,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
   <cs:axisTitle>
@@ -2905,6 +3389,526 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3529,6 +4533,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>553861</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>118886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>248709</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>83961</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54045EFC-0DF9-0EB3-B179-5F1F511F299F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3865,7 +4905,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:52" ht="24.5" x14ac:dyDescent="0.65">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="21" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3876,31 +4916,31 @@
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="27" t="s">
+      <c r="K4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="19" t="s">
         <v>13</v>
       </c>
       <c r="O4" s="26" t="s">
@@ -3909,34 +4949,34 @@
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
       <c r="R4" s="26"/>
-      <c r="S4" s="27" t="s">
+      <c r="S4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="27" t="s">
+      <c r="T4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="27" t="s">
+      <c r="U4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="27" t="s">
+      <c r="V4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="27" t="s">
+      <c r="W4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="X4" s="27" t="s">
+      <c r="X4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="Y4" s="27" t="s">
+      <c r="Y4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="27" t="s">
+      <c r="Z4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="AA4" s="27" t="s">
+      <c r="AA4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AB4" s="19" t="s">
         <v>13</v>
       </c>
       <c r="AD4" s="26" t="s">
@@ -3945,22 +4985,22 @@
       <c r="AE4" s="26"/>
       <c r="AF4" s="26"/>
       <c r="AG4" s="26"/>
-      <c r="AH4" s="27" t="s">
+      <c r="AH4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="AI4" s="27" t="s">
+      <c r="AI4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="AJ4" s="27" t="s">
+      <c r="AJ4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="AK4" s="27" t="s">
+      <c r="AK4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="AL4" s="27" t="s">
+      <c r="AL4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="AM4" s="27" t="s">
+      <c r="AM4" s="19" t="s">
         <v>13</v>
       </c>
       <c r="AO4" s="26" t="s">
@@ -3968,37 +5008,37 @@
       </c>
       <c r="AP4" s="26"/>
       <c r="AQ4" s="26"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27" t="s">
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="19"/>
+      <c r="AT4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="AU4" s="27" t="s">
+      <c r="AU4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="AV4" s="27" t="s">
+      <c r="AV4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="AW4" s="27" t="s">
+      <c r="AW4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="AX4" s="27" t="s">
+      <c r="AX4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="AY4" s="27" t="s">
+      <c r="AY4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="AZ4" s="27" t="s">
+      <c r="AZ4" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="21"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="3">
         <v>0</v>
       </c>
@@ -4029,12 +5069,12 @@
         <f>ABS(($C$7-H5)/$C$7)</f>
         <v>0.13394919168591224</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="20"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="22"/>
       <c r="S5" s="3">
         <v>0</v>
       </c>
@@ -4053,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="X5" s="2">
-        <f>T5-((U5-T5)/(W5-V5))*V5</f>
+        <f t="shared" ref="X5:X11" si="0">T5-((U5-T5)/(W5-V5))*V5</f>
         <v>1.6666666666666665</v>
       </c>
       <c r="Y5" s="2">
@@ -4061,20 +5101,20 @@
         <v>-0.22222222222222276</v>
       </c>
       <c r="Z5" s="2">
-        <f>V5*Y5</f>
+        <f t="shared" ref="Z5:Z11" si="1">V5*Y5</f>
         <v>0.44444444444444553</v>
       </c>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2">
-        <f>ABS(($Q$7-X5)/$Q$7)</f>
+        <f t="shared" ref="AB5:AB11" si="2">ABS(($Q$7-X5)/$Q$7)</f>
         <v>3.7721324095458121E-2</v>
       </c>
-      <c r="AD5" s="19" t="s">
+      <c r="AD5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="19"/>
-      <c r="AG5" s="20"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="22"/>
       <c r="AH5" s="3">
         <v>0</v>
       </c>
@@ -4095,12 +5135,12 @@
         <f>ABS($AF$8-AI5)/$AF$8</f>
         <v>0.13394919168591224</v>
       </c>
-      <c r="AO5" s="19" t="s">
+      <c r="AO5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="AP5" s="19"/>
-      <c r="AQ5" s="19"/>
-      <c r="AR5" s="20"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="22"/>
       <c r="AS5" s="2" t="s">
         <v>23</v>
       </c>
@@ -4119,21 +5159,21 @@
         <f>ABS($AQ$6-AU5)/$AQ$6</f>
         <v>0.42263279445727481</v>
       </c>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29">
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20">
         <f>AX5</f>
         <v>0.42263279445727481</v>
       </c>
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="3">
         <v>1</v>
       </c>
@@ -4166,26 +5206,26 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" ref="M6:M23" si="0">ABS(($C$7-H6)/$C$7)</f>
+        <f t="shared" ref="M6:M23" si="3">ABS(($C$7-H6)/$C$7)</f>
         <v>1.0392609699769063E-2</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="s">
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="20"/>
+      <c r="R6" s="22"/>
       <c r="S6" s="3">
         <v>1</v>
       </c>
       <c r="T6" s="2">
-        <f>IF(Z5&lt;0,T5,X5)</f>
+        <f t="shared" ref="T6:T11" si="4">IF(Z5&lt;0,T5,X5)</f>
         <v>1.6666666666666665</v>
       </c>
       <c r="U6" s="2">
-        <f>IF(Z5&gt;0,U5,X5)</f>
+        <f t="shared" ref="U6:U11" si="5">IF(Z5&gt;0,U5,X5)</f>
         <v>2</v>
       </c>
       <c r="V6" s="2">
@@ -4197,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="2">
-        <f>T6-((U6-T6)/(W6-V6))*V6</f>
+        <f t="shared" si="0"/>
         <v>1.7272727272727273</v>
       </c>
       <c r="Y6" s="2">
@@ -4205,23 +5245,23 @@
         <v>-1.6528925619834656E-2</v>
       </c>
       <c r="Z6" s="2">
-        <f>V6*Y6</f>
+        <f t="shared" si="1"/>
         <v>3.6730945821854882E-3</v>
       </c>
       <c r="AA6" s="2">
-        <f>ABS((X6-T6)/X6)</f>
+        <f t="shared" ref="AA6:AA11" si="6">ABS((X6-T6)/X6)</f>
         <v>3.5087719298245709E-2</v>
       </c>
       <c r="AB6" s="2">
-        <f>ABS(($Q$7-X6)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>2.7293722443837709E-3</v>
       </c>
-      <c r="AD6" s="19" t="s">
+      <c r="AD6" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="20"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="22"/>
       <c r="AH6" s="3">
         <v>1</v>
       </c>
@@ -4245,14 +5285,14 @@
         <f>ABS($AF$8-AI6)/$AF$8</f>
         <v>1.0392609699769063E-2</v>
       </c>
-      <c r="AO6" s="19" t="s">
+      <c r="AO6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="AP6" s="19"/>
-      <c r="AQ6" s="19">
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27">
         <v>1.732</v>
       </c>
-      <c r="AR6" s="20"/>
+      <c r="AR6" s="22"/>
       <c r="AS6" s="2" t="s">
         <v>24</v>
       </c>
@@ -4274,76 +5314,76 @@
         <f>ABS($AQ$6-AU6)/$AQ$6</f>
         <v>0.15473441108545036</v>
       </c>
-      <c r="AY6" s="29">
+      <c r="AY6" s="20">
         <f>AW6</f>
         <v>0.5</v>
       </c>
-      <c r="AZ6" s="29">
-        <f t="shared" ref="AZ6:AZ10" si="1">AX6</f>
+      <c r="AZ6" s="20">
+        <f t="shared" ref="AZ6:AZ10" si="7">AX6</f>
         <v>0.15473441108545036</v>
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="22">
+      <c r="B7" s="27"/>
+      <c r="C7" s="24">
         <v>1.732</v>
       </c>
-      <c r="D7" s="23"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="3">
         <v>2</v>
       </c>
       <c r="F7" s="3">
-        <f t="shared" ref="F7:F10" si="2">IF(K6&lt;0,F6,H6)</f>
+        <f t="shared" ref="F7:F10" si="8">IF(K6&lt;0,F6,H6)</f>
         <v>1.5</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" ref="G7:G12" si="3">IF(K6&gt;0,G6,H6)</f>
+        <f t="shared" ref="G7:G12" si="9">IF(K6&gt;0,G6,H6)</f>
         <v>1.75</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" ref="H7:H10" si="4">(F7+G7)/2</f>
+        <f t="shared" ref="H7:H10" si="10">(F7+G7)/2</f>
         <v>1.625</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" ref="I7:I10" si="5">(F7)^2-3</f>
+        <f t="shared" ref="I7:I10" si="11">(F7)^2-3</f>
         <v>-0.75</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" ref="J7:J10" si="6">(H7)^2-3</f>
+        <f t="shared" ref="J7:J10" si="12">(H7)^2-3</f>
         <v>-0.359375</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" ref="K7:K10" si="7">(I7)*(J7)</f>
+        <f t="shared" ref="K7:K10" si="13">(I7)*(J7)</f>
         <v>0.26953125</v>
       </c>
       <c r="L7" s="2">
-        <f t="shared" ref="L7:L23" si="8">ABS((H7-F7)/H7)</f>
+        <f t="shared" ref="L7:L23" si="14">ABS((H7-F7)/H7)</f>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="M7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.1778290993071583E-2</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="24">
+      <c r="P7" s="27"/>
+      <c r="Q7" s="28">
         <v>1.732</v>
       </c>
-      <c r="R7" s="22"/>
+      <c r="R7" s="24"/>
       <c r="S7" s="3">
         <v>2</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(Z6&lt;0,T6,X6)</f>
+        <f t="shared" si="4"/>
         <v>1.7272727272727273</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(Z6&gt;0,U6,X6)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V7" s="2">
@@ -4351,54 +5391,54 @@
         <v>-1.6528925619834656E-2</v>
       </c>
       <c r="W7" s="2">
-        <f t="shared" ref="W7:W11" si="9">U7^2-3</f>
+        <f t="shared" ref="W7:W11" si="15">U7^2-3</f>
         <v>1</v>
       </c>
       <c r="X7" s="2">
-        <f>T7-((U7-T7)/(W7-V7))*V7</f>
+        <f t="shared" si="0"/>
         <v>1.7317073170731707</v>
       </c>
       <c r="Y7" s="2">
-        <f t="shared" ref="Y7:Y11" si="10">X7^2-3</f>
+        <f t="shared" ref="Y7:Y11" si="16">X7^2-3</f>
         <v>-1.1897679952408424E-3</v>
       </c>
       <c r="Z7" s="2">
-        <f>V7*Y7</f>
+        <f t="shared" si="1"/>
         <v>1.9665586698195677E-5</v>
       </c>
       <c r="AA7" s="2">
-        <f>ABS((X7-T7)/X7)</f>
+        <f t="shared" si="6"/>
         <v>2.560819462227892E-3</v>
       </c>
       <c r="AB7" s="2">
-        <f>ABS(($Q$7-X7)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>1.6898552357348068E-4</v>
       </c>
-      <c r="AD7" s="19" t="s">
+      <c r="AD7" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19">
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="27">
         <v>1.5</v>
       </c>
-      <c r="AG7" s="20"/>
+      <c r="AG7" s="22"/>
       <c r="AH7" s="3">
         <v>2</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" ref="AI7" si="11">AI6-(AJ6/AK6)</f>
+        <f t="shared" ref="AI7" si="17">AI6-(AJ6/AK6)</f>
         <v>1.7321428571428572</v>
       </c>
       <c r="AJ7" s="12">
-        <f t="shared" ref="AJ7:AJ8" si="12">AI7^2-3</f>
+        <f t="shared" ref="AJ7:AJ8" si="18">AI7^2-3</f>
         <v>3.1887755102077975E-4</v>
       </c>
       <c r="AK7" s="2">
-        <f t="shared" ref="AK7:AK8" si="13">2*AI7</f>
+        <f t="shared" ref="AK7:AK8" si="19">2*AI7</f>
         <v>3.4642857142857144</v>
       </c>
       <c r="AL7" s="11">
-        <f t="shared" ref="AL7" si="14">ABS(AI7-AI6)/AI7</f>
+        <f t="shared" ref="AL7" si="20">ABS(AI7-AI6)/AI7</f>
         <v>1.0309278350515427E-2</v>
       </c>
       <c r="AM7" s="2">
@@ -4420,19 +5460,19 @@
         <v>-0.22222222222222188</v>
       </c>
       <c r="AW7" s="2">
-        <f t="shared" ref="AW7:AW10" si="15">ABS(AU7-AU6)/AU7</f>
+        <f t="shared" ref="AW7:AW10" si="21">ABS(AU7-AU6)/AU7</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AX7" s="2">
-        <f t="shared" ref="AX7:AX10" si="16">ABS($AQ$6-AU7)/$AQ$6</f>
+        <f t="shared" ref="AX7:AX10" si="22">ABS($AQ$6-AU7)/$AQ$6</f>
         <v>3.7721324095457996E-2</v>
       </c>
-      <c r="AY7" s="29">
-        <f t="shared" ref="AY7:AY10" si="17">AW7</f>
+      <c r="AY7" s="20">
+        <f t="shared" ref="AY7:AY10" si="23">AW7</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AZ7" s="29">
-        <f t="shared" si="1"/>
+      <c r="AZ7" s="20">
+        <f t="shared" si="7"/>
         <v>3.7721324095457996E-2</v>
       </c>
     </row>
@@ -4449,38 +5489,38 @@
         <v>1.75</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1.6875</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>-0.359375</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>-0.15234375</v>
       </c>
       <c r="K8" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>5.474853515625E-2</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>3.7037037037037035E-2</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.5692840646651262E-2</v>
       </c>
       <c r="S8" s="3">
         <v>3</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(Z7&lt;0,T7,X7)</f>
+        <f t="shared" si="4"/>
         <v>1.7317073170731707</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(Z7&gt;0,U7,X7)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V8" s="2">
@@ -4488,37 +5528,37 @@
         <v>-1.1897679952408424E-3</v>
       </c>
       <c r="W8" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="X8" s="2">
-        <f>T8-((U8-T8)/(W8-V8))*V8</f>
+        <f t="shared" si="0"/>
         <v>1.7320261437908497</v>
       </c>
       <c r="Y8" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-8.5437224998763384E-5</v>
       </c>
       <c r="Z8" s="2">
-        <f>V8*Y8</f>
+        <f t="shared" si="1"/>
         <v>1.016504759057195E-7</v>
       </c>
       <c r="AA8" s="2">
-        <f>ABS((X8-T8)/X8)</f>
+        <f t="shared" si="6"/>
         <v>1.8407731247128416E-4</v>
       </c>
       <c r="AB8" s="2">
-        <f>ABS(($Q$7-X8)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>1.5094567465215385E-5</v>
       </c>
-      <c r="AD8" s="19" t="s">
+      <c r="AD8" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="19">
+      <c r="AE8" s="27"/>
+      <c r="AF8" s="27">
         <v>1.732</v>
       </c>
-      <c r="AG8" s="20"/>
+      <c r="AG8" s="22"/>
       <c r="AH8" s="3">
         <v>3</v>
       </c>
@@ -4527,11 +5567,11 @@
         <v>1.7320508100147276</v>
       </c>
       <c r="AJ8" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>8.4726741178542397E-9</v>
       </c>
       <c r="AK8" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>3.4641016200294552</v>
       </c>
       <c r="AL8" s="11">
@@ -4550,7 +5590,7 @@
         <v>1.7272727272727273</v>
       </c>
       <c r="AV8" s="10">
-        <f t="shared" ref="AV8:AV10" si="18">AU8^2-3</f>
+        <f t="shared" ref="AV8:AV10" si="24">AU8^2-3</f>
         <v>-1.6528925619834656E-2</v>
       </c>
       <c r="AW8" s="2">
@@ -4558,15 +5598,15 @@
         <v>3.5087719298245584E-2</v>
       </c>
       <c r="AX8" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.7293722443837709E-3</v>
       </c>
-      <c r="AY8" s="29">
-        <f t="shared" si="17"/>
+      <c r="AY8" s="20">
+        <f t="shared" si="23"/>
         <v>3.5087719298245584E-2</v>
       </c>
-      <c r="AZ8" s="29">
-        <f t="shared" si="1"/>
+      <c r="AZ8" s="20">
+        <f t="shared" si="7"/>
         <v>2.7293722443837709E-3</v>
       </c>
     </row>
@@ -4583,38 +5623,38 @@
         <v>1.75</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v>1.71875</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>-0.15234375</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>-4.58984375E-2</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>6.992340087890625E-3</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>1.8181818181818181E-2</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.6501154734410996E-3</v>
       </c>
       <c r="S9" s="3">
         <v>4</v>
       </c>
       <c r="T9" s="2">
-        <f>IF(Z8&lt;0,T8,X8)</f>
+        <f t="shared" si="4"/>
         <v>1.7320261437908497</v>
       </c>
       <c r="U9" s="2">
-        <f>IF(Z8&gt;0,U8,X8)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V9" s="2">
@@ -4622,27 +5662,27 @@
         <v>-8.5437224998763384E-5</v>
       </c>
       <c r="W9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="X9" s="2">
-        <f>T9-((U9-T9)/(W9-V9))*V9</f>
+        <f t="shared" si="0"/>
         <v>1.7320490367775832</v>
       </c>
       <c r="Y9" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-6.1341978465634384E-6</v>
       </c>
       <c r="Z9" s="2">
-        <f>V9*Y9</f>
+        <f t="shared" si="1"/>
         <v>5.2408884160377034E-10</v>
       </c>
       <c r="AA9" s="2">
-        <f>ABS((X9-T9)/X9)</f>
+        <f t="shared" si="6"/>
         <v>1.3217285566005327E-5</v>
       </c>
       <c r="AB9" s="2">
-        <f>ABS(($Q$7-X9)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>2.8312227242013177E-5</v>
       </c>
       <c r="AH9" s="6">
@@ -4676,7 +5716,7 @@
         <v>1.7321428571428572</v>
       </c>
       <c r="AV9" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>3.1887755102077975E-4</v>
       </c>
       <c r="AW9" s="2">
@@ -4684,15 +5724,15 @@
         <v>2.811621368322424E-3</v>
       </c>
       <c r="AX9" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>8.2481029363292314E-5</v>
       </c>
-      <c r="AY9" s="29">
-        <f t="shared" si="17"/>
+      <c r="AY9" s="20">
+        <f t="shared" si="23"/>
         <v>2.811621368322424E-3</v>
       </c>
-      <c r="AZ9" s="29">
-        <f t="shared" si="1"/>
+      <c r="AZ9" s="20">
+        <f t="shared" si="7"/>
         <v>8.2481029363292314E-5</v>
       </c>
     </row>
@@ -4701,46 +5741,46 @@
         <v>5</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>1.71875</v>
       </c>
       <c r="G10" s="3">
+        <f t="shared" si="9"/>
+        <v>1.75</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="10"/>
+        <v>1.734375</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="11"/>
+        <v>-4.58984375E-2</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="12"/>
+        <v>8.056640625E-3</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="13"/>
+        <v>-3.6978721618652344E-4</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="14"/>
+        <v>9.0090090090090089E-3</v>
+      </c>
+      <c r="M10" s="2">
         <f t="shared" si="3"/>
-        <v>1.75</v>
-      </c>
-      <c r="H10" s="4">
-        <f t="shared" si="4"/>
-        <v>1.734375</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="5"/>
-        <v>-4.58984375E-2</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="6"/>
-        <v>8.056640625E-3</v>
-      </c>
-      <c r="K10" s="2">
-        <f t="shared" si="7"/>
-        <v>-3.6978721618652344E-4</v>
-      </c>
-      <c r="L10" s="2">
-        <f t="shared" si="8"/>
-        <v>9.0090090090090089E-3</v>
-      </c>
-      <c r="M10" s="2">
-        <f t="shared" si="0"/>
         <v>1.3712471131639816E-3</v>
       </c>
       <c r="S10" s="6">
         <v>5</v>
       </c>
       <c r="T10" s="5">
-        <f>IF(Z9&lt;0,T9,X9)</f>
+        <f t="shared" si="4"/>
         <v>1.7320490367775832</v>
       </c>
       <c r="U10" s="5">
-        <f>IF(Z9&gt;0,U9,X9)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V10" s="5">
@@ -4748,27 +5788,27 @@
         <v>-6.1341978465634384E-6</v>
       </c>
       <c r="W10" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="X10" s="5">
-        <f>T10-((U10-T10)/(W10-V10))*V10</f>
+        <f t="shared" si="0"/>
         <v>1.7320506804317222</v>
       </c>
       <c r="Y10" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-4.4041600810729165E-7</v>
       </c>
       <c r="Z10" s="5">
-        <f>V10*Y10</f>
+        <f t="shared" si="1"/>
         <v>2.7015989285238144E-12</v>
       </c>
       <c r="AA10" s="5">
-        <f>ABS((X10-T10)/X10)</f>
+        <f t="shared" si="6"/>
         <v>9.4896422927224018E-7</v>
       </c>
       <c r="AB10" s="5">
-        <f>ABS(($Q$7-X10)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>2.9261219239135781E-5</v>
       </c>
       <c r="AT10" s="5">
@@ -4779,23 +5819,23 @@
         <v>1.7320506804317222</v>
       </c>
       <c r="AV10" s="18">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>-4.4041600810729165E-7</v>
       </c>
       <c r="AW10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>5.32182528931911E-5</v>
       </c>
       <c r="AX10" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.9261219239135781E-5</v>
       </c>
-      <c r="AY10" s="29">
-        <f t="shared" si="17"/>
+      <c r="AY10" s="20">
+        <f t="shared" si="23"/>
         <v>5.32182528931911E-5</v>
       </c>
-      <c r="AZ10" s="29">
-        <f t="shared" si="1"/>
+      <c r="AZ10" s="20">
+        <f t="shared" si="7"/>
         <v>2.9261219239135781E-5</v>
       </c>
     </row>
@@ -4804,46 +5844,46 @@
         <v>6</v>
       </c>
       <c r="F11" s="3">
-        <f t="shared" ref="F11:F18" si="19">IF(K10&lt;0,F10,H10)</f>
+        <f t="shared" ref="F11:F18" si="25">IF(K10&lt;0,F10,H10)</f>
         <v>1.71875</v>
       </c>
       <c r="G11" s="3">
+        <f t="shared" si="9"/>
+        <v>1.734375</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" ref="H11:H19" si="26">(F11+G11)/2</f>
+        <v>1.7265625</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" ref="I11:I19" si="27">(F11)^2-3</f>
+        <v>-4.58984375E-2</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" ref="J11:J19" si="28">(H11)^2-3</f>
+        <v>-1.898193359375E-2</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" ref="K11:K19" si="29">(I11)*(J11)</f>
+        <v>8.7124109268188477E-4</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="14"/>
+        <v>4.5248868778280547E-3</v>
+      </c>
+      <c r="M11" s="2">
         <f t="shared" si="3"/>
-        <v>1.734375</v>
-      </c>
-      <c r="H11" s="4">
-        <f t="shared" ref="H11:H19" si="20">(F11+G11)/2</f>
-        <v>1.7265625</v>
-      </c>
-      <c r="I11" s="3">
-        <f t="shared" ref="I11:I19" si="21">(F11)^2-3</f>
-        <v>-4.58984375E-2</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" ref="J11:J19" si="22">(H11)^2-3</f>
-        <v>-1.898193359375E-2</v>
-      </c>
-      <c r="K11" s="2">
-        <f t="shared" ref="K11:K19" si="23">(I11)*(J11)</f>
-        <v>8.7124109268188477E-4</v>
-      </c>
-      <c r="L11" s="2">
-        <f t="shared" si="8"/>
-        <v>4.5248868778280547E-3</v>
-      </c>
-      <c r="M11" s="2">
-        <f t="shared" si="0"/>
         <v>3.139434180138559E-3</v>
       </c>
       <c r="S11" s="6">
         <v>6</v>
       </c>
       <c r="T11" s="5">
-        <f>IF(Z10&lt;0,T10,X10)</f>
+        <f t="shared" si="4"/>
         <v>1.7320506804317222</v>
       </c>
       <c r="U11" s="5">
-        <f>IF(Z10&gt;0,U10,X10)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="V11" s="5">
@@ -4851,27 +5891,27 @@
         <v>-4.4041600810729165E-7</v>
       </c>
       <c r="W11" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="X11" s="5">
-        <f>T11-((U11-T11)/(W11-V11))*V11</f>
+        <f t="shared" si="0"/>
         <v>1.73205079844084</v>
       </c>
       <c r="Y11" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>-3.162044892590643E-8</v>
       </c>
       <c r="Z11" s="5">
-        <f>V11*Y11</f>
+        <f t="shared" si="1"/>
         <v>1.3926151890508208E-14</v>
       </c>
       <c r="AA11" s="5">
-        <f>ABS((X11-T11)/X11)</f>
+        <f t="shared" si="6"/>
         <v>6.8132596294082609E-8</v>
       </c>
       <c r="AB11" s="5">
-        <f>ABS(($Q$7-X11)/$Q$7)</f>
+        <f t="shared" si="2"/>
         <v>2.9329353833714888E-5</v>
       </c>
       <c r="AU11" s="15"/>
@@ -4882,35 +5922,35 @@
         <v>7</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.7265625</v>
       </c>
       <c r="G12" s="3">
+        <f t="shared" si="9"/>
+        <v>1.734375</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="26"/>
+        <v>1.73046875</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="27"/>
+        <v>-1.898193359375E-2</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="28"/>
+        <v>-5.4779052734375E-3</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="29"/>
+        <v>1.0398123413324356E-4</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="14"/>
+        <v>2.257336343115124E-3</v>
+      </c>
+      <c r="M12" s="2">
         <f t="shared" si="3"/>
-        <v>1.734375</v>
-      </c>
-      <c r="H12" s="4">
-        <f t="shared" si="20"/>
-        <v>1.73046875</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="21"/>
-        <v>-1.898193359375E-2</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="22"/>
-        <v>-5.4779052734375E-3</v>
-      </c>
-      <c r="K12" s="2">
-        <f t="shared" si="23"/>
-        <v>1.0398123413324356E-4</v>
-      </c>
-      <c r="L12" s="2">
-        <f t="shared" si="8"/>
-        <v>2.257336343115124E-3</v>
-      </c>
-      <c r="M12" s="2">
-        <f t="shared" si="0"/>
         <v>8.8409353348728871E-4</v>
       </c>
     </row>
@@ -4919,35 +5959,35 @@
         <v>8</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.73046875</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" ref="G13:G19" si="24">IF(K12&gt;0,G12,H12)</f>
+        <f t="shared" ref="G13:G19" si="30">IF(K12&gt;0,G12,H12)</f>
         <v>1.734375</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.732421875</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-5.4779052734375E-3</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.285552978515625E-3</v>
       </c>
       <c r="K13" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-7.0421374402940273E-6</v>
       </c>
       <c r="L13" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>1.1273957158962795E-3</v>
       </c>
       <c r="M13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.4357678983834641E-4</v>
       </c>
     </row>
@@ -4956,35 +5996,35 @@
         <v>9</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.73046875</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.732421875</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.7314453125</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-5.4779052734375E-3</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-2.0971298217773438E-3</v>
       </c>
       <c r="K14" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>1.1487878509797156E-5</v>
       </c>
       <c r="L14" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>5.6401579244218843E-4</v>
       </c>
       <c r="M14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.2025837182447114E-4</v>
       </c>
     </row>
@@ -4993,35 +6033,35 @@
         <v>10</v>
       </c>
       <c r="F15" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.7314453125</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.732421875</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.73193359375</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-2.0971298217773438E-3</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-4.0602684020996094E-4</v>
       </c>
       <c r="K15" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>8.5149099504633341E-7</v>
       </c>
       <c r="L15" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>2.8192839018889202E-4</v>
       </c>
       <c r="M15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.8340790993062366E-5</v>
       </c>
     </row>
@@ -5030,35 +6070,35 @@
         <v>11</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.73193359375</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.732421875</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.732177734375</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-4.0602684020996094E-4</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>4.3970346450805664E-4</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-1.7853140832357894E-7</v>
       </c>
       <c r="L16" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>1.4094432699083862E-4</v>
       </c>
       <c r="M16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0261799942264203E-4</v>
       </c>
     </row>
@@ -5067,35 +6107,35 @@
         <v>12</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.73193359375</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.732177734375</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.7320556640625</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-4.0602684020996094E-4</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>1.6823410987854004E-5</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>-6.8307564049518987E-9</v>
       </c>
       <c r="L17" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>7.0477130171259429E-5</v>
       </c>
       <c r="M17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.2138604214789831E-5</v>
       </c>
     </row>
@@ -5104,35 +6144,35 @@
         <v>13</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1.73193359375</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.7320556640625</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.73199462890625</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-4.0602684020996094E-4</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-1.9460543990135193E-4</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>7.9015031850815376E-8</v>
       </c>
       <c r="L18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>3.5239806885858265E-5</v>
       </c>
       <c r="M18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.1010933891362659E-6</v>
       </c>
     </row>
@@ -5145,31 +6185,31 @@
         <v>1.73199462890625</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.7320556640625</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1.732025146484375</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-1.9460543990135193E-4</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>-8.8891945779323578E-5</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>1.7298856212072389E-8</v>
       </c>
       <c r="L19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>1.7619592987401992E-5</v>
       </c>
       <c r="M19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.4518755412826783E-5</v>
       </c>
     </row>
@@ -5178,35 +6218,35 @@
         <v>15</v>
       </c>
       <c r="F20" s="3">
-        <f t="shared" ref="F20:F23" si="25">IF(K19&lt;0,F19,H19)</f>
+        <f t="shared" ref="F20:F23" si="31">IF(K19&lt;0,F19,H19)</f>
         <v>1.732025146484375</v>
       </c>
       <c r="G20" s="3">
-        <f t="shared" ref="G20:G23" si="26">IF(K19&gt;0,G19,H19)</f>
+        <f t="shared" ref="G20:G23" si="32">IF(K19&gt;0,G19,H19)</f>
         <v>1.7320556640625</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" ref="H20:H23" si="27">(F20+G20)/2</f>
+        <f t="shared" ref="H20:H23" si="33">(F20+G20)/2</f>
         <v>1.7320404052734375</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" ref="I20:I23" si="28">(F20)^2-3</f>
+        <f t="shared" ref="I20:I23" si="34">(F20)^2-3</f>
         <v>-8.8891945779323578E-5</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:J23" si="29">(H20)^2-3</f>
+        <f t="shared" ref="J20:J23" si="35">(H20)^2-3</f>
         <v>-3.6034500226378441E-5</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" ref="K20:K23" si="30">(I20)*(J20)</f>
+        <f t="shared" ref="K20:K23" si="36">(I20)*(J20)</f>
         <v>3.2031768403082556E-9</v>
       </c>
       <c r="L20" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>8.8097188818704796E-6</v>
       </c>
       <c r="M20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.3328679813808309E-5</v>
       </c>
     </row>
@@ -5215,35 +6255,35 @@
         <v>16</v>
       </c>
       <c r="F21" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1.7320404052734375</v>
       </c>
       <c r="G21" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.7320556640625</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>1.7320480346679688</v>
       </c>
       <c r="I21" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>-3.6034500226378441E-5</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>-9.6056028269231319E-6</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>3.4613309724126299E-10</v>
       </c>
       <c r="L21" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>4.4048400382340118E-6</v>
       </c>
       <c r="M21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.7733642014299068E-5</v>
       </c>
     </row>
@@ -5252,35 +6292,35 @@
         <v>17</v>
       </c>
       <c r="F22" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1.7320480346679688</v>
       </c>
       <c r="G22" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.7320556640625</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>1.7320518493652344</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>-9.6056028269231319E-6</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>3.6088895285502076E-6</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>-3.4665559457495163E-11</v>
       </c>
       <c r="L22" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>2.2024151684737483E-6</v>
       </c>
       <c r="M22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.9936123114544451E-5</v>
       </c>
     </row>
@@ -5289,35 +6329,35 @@
         <v>18</v>
       </c>
       <c r="F23" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1.7320480346679688</v>
       </c>
       <c r="G23" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>1.7320518493652344</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>1.7320499420166016</v>
       </c>
       <c r="I23" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>-9.6056028269231319E-6</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>-2.9983602871652693E-6</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>2.8801058050528764E-11</v>
       </c>
       <c r="L23" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>1.1012087968963532E-6</v>
       </c>
       <c r="M23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.8834882564421761E-5</v>
       </c>
     </row>
@@ -5326,35 +6366,35 @@
         <v>19</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" ref="F24:F27" si="31">IF(K23&lt;0,F23,H23)</f>
+        <f t="shared" ref="F24:F27" si="37">IF(K23&lt;0,F23,H23)</f>
         <v>1.7320499420166016</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" ref="G24:G27" si="32">IF(K23&gt;0,G23,H23)</f>
+        <f t="shared" ref="G24:G27" si="38">IF(K23&gt;0,G23,H23)</f>
         <v>1.7320518493652344</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" ref="H24:H27" si="33">(F24+G24)/2</f>
+        <f t="shared" ref="H24:H27" si="39">(F24+G24)/2</f>
         <v>1.732050895690918</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" ref="I24:I27" si="34">(F24)^2-3</f>
+        <f t="shared" ref="I24:I27" si="40">(F24)^2-3</f>
         <v>-2.9983602871652693E-6</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:J27" si="35">(H24)^2-3</f>
+        <f t="shared" ref="J24:J27" si="41">(H24)^2-3</f>
         <v>3.0526371119776741E-7</v>
       </c>
       <c r="K24" s="2">
-        <f t="shared" ref="K24:K27" si="36">(I24)*(J24)</f>
+        <f t="shared" ref="K24:K27" si="42">(I24)*(J24)</f>
         <v>-9.152905887680737E-13</v>
       </c>
       <c r="L24" s="2">
-        <f t="shared" ref="L24:L27" si="37">ABS((H24-F24)/H24)</f>
+        <f t="shared" ref="L24:L27" si="43">ABS((H24-F24)/H24)</f>
         <v>5.5060409528313993E-7</v>
       </c>
       <c r="M24" s="2">
-        <f t="shared" ref="M24:M27" si="38">ABS(($C$7-H24)/$C$7)</f>
+        <f t="shared" ref="M24:M27" si="44">ABS(($C$7-H24)/$C$7)</f>
         <v>2.9385502839483106E-5</v>
       </c>
     </row>
@@ -5363,35 +6403,35 @@
         <v>20</v>
       </c>
       <c r="F25" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.7320499420166016</v>
       </c>
       <c r="G25" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>1.732050895690918</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>1.7320504188537598</v>
       </c>
       <c r="I25" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>-2.9983602871652693E-6</v>
       </c>
       <c r="J25" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>-1.3465485153574264E-6</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>4.0374375931890599E-12</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>2.7530212343280827E-7</v>
       </c>
       <c r="M25" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>2.9110192701952432E-5</v>
       </c>
     </row>
@@ -5400,35 +6440,35 @@
         <v>21</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.7320504188537598</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>1.732050895690918</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>1.7320506572723389</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>-1.3465485153574264E-6</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>-5.2064245892324834E-7</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>7.010703300951399E-13</v>
       </c>
       <c r="L26" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>1.3765104276859194E-7</v>
       </c>
       <c r="M26" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>2.9247847770717769E-5</v>
       </c>
     </row>
@@ -5437,35 +6477,35 @@
         <v>22</v>
       </c>
       <c r="F27" s="3">
-        <f t="shared" si="31"/>
+        <f t="shared" si="37"/>
         <v>1.7320506572723389</v>
       </c>
       <c r="G27" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>1.732050895690918</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>1.7320507764816284</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>-5.2064245892324834E-7</v>
       </c>
       <c r="J27" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>-1.0768938807359518E-7</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>5.606766780657653E-14</v>
       </c>
       <c r="L27" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v>6.8825516647343899E-8</v>
       </c>
       <c r="M27" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v>2.9316675305100436E-5</v>
       </c>
     </row>
@@ -5474,35 +6514,35 @@
         <v>23</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" ref="F28:F31" si="39">IF(K27&lt;0,F27,H27)</f>
+        <f t="shared" ref="F28:F31" si="45">IF(K27&lt;0,F27,H27)</f>
         <v>1.7320507764816284</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" ref="G28:G31" si="40">IF(K27&gt;0,G27,H27)</f>
+        <f t="shared" ref="G28:G31" si="46">IF(K27&gt;0,G27,H27)</f>
         <v>1.732050895690918</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" ref="H28:H31" si="41">(F28+G28)/2</f>
+        <f t="shared" ref="H28:H31" si="47">(F28+G28)/2</f>
         <v>1.7320508360862732</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" ref="I28:I31" si="42">(F28)^2-3</f>
+        <f t="shared" ref="I28:I31" si="48">(F28)^2-3</f>
         <v>-1.0768938807359518E-7</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28:J31" si="43">(H28)^2-3</f>
+        <f t="shared" ref="J28:J31" si="49">(H28)^2-3</f>
         <v>9.8787158009372433E-8</v>
       </c>
       <c r="K28" s="2">
-        <f t="shared" ref="K28:K31" si="44">(I28)*(J28)</f>
+        <f t="shared" ref="K28:K31" si="50">(I28)*(J28)</f>
         <v>-1.0638328595558875E-14</v>
       </c>
       <c r="L28" s="2">
-        <f t="shared" ref="L28:L31" si="45">ABS((H28-F28)/H28)</f>
+        <f t="shared" ref="L28:L31" si="51">ABS((H28-F28)/H28)</f>
         <v>3.4412757139434054E-8</v>
       </c>
       <c r="M28" s="2">
-        <f t="shared" ref="M28:M31" si="46">ABS(($C$7-H28)/$C$7)</f>
+        <f t="shared" ref="M28:M31" si="52">ABS(($C$7-H28)/$C$7)</f>
         <v>2.9351089072291769E-5</v>
       </c>
     </row>
@@ -5511,35 +6551,35 @@
         <v>24</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>1.7320507764816284</v>
       </c>
       <c r="G29" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>1.7320508360862732</v>
       </c>
       <c r="H29" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.7320508062839508</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>-1.0768938807359518E-7</v>
       </c>
       <c r="J29" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>4.7933794970064542E-16</v>
       </c>
       <c r="L29" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>1.7206378865776496E-8</v>
       </c>
       <c r="M29" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>2.9333882188696103E-5</v>
       </c>
     </row>
@@ -5548,35 +6588,35 @@
         <v>25</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>1.7320508062839508</v>
       </c>
       <c r="G30" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>1.7320508360862732</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.732050821185112</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>4.716802060045211E-8</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-2.0995032742322937E-16</v>
       </c>
       <c r="L30" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>8.6031893588733808E-9</v>
       </c>
       <c r="M30" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>2.9342485630493936E-5</v>
       </c>
     </row>
@@ -5585,35 +6625,35 @@
         <v>26</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v>1.7320508062839508</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v>1.732050821185112</v>
       </c>
       <c r="H31" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="47"/>
         <v>1.7320508137345314</v>
       </c>
       <c r="I31" s="3">
-        <f t="shared" si="42"/>
+        <f t="shared" si="48"/>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="J31" s="3">
-        <f t="shared" si="43"/>
+        <f t="shared" si="49"/>
         <v>2.1358452340081158E-8</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>-9.5068947243686053E-17</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" si="45"/>
+        <f t="shared" si="51"/>
         <v>4.3015946979404072E-9</v>
       </c>
       <c r="M31" s="2">
-        <f t="shared" si="46"/>
+        <f t="shared" si="52"/>
         <v>2.9338183909595021E-5</v>
       </c>
     </row>
@@ -5622,35 +6662,35 @@
         <v>27</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" ref="F32:F38" si="47">IF(K31&lt;0,F31,H31)</f>
+        <f t="shared" ref="F32:F38" si="53">IF(K31&lt;0,F31,H31)</f>
         <v>1.7320508062839508</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" ref="G32:G38" si="48">IF(K31&gt;0,G31,H31)</f>
+        <f t="shared" ref="G32:G38" si="54">IF(K31&gt;0,G31,H31)</f>
         <v>1.7320508137345314</v>
       </c>
       <c r="H32" s="4">
-        <f t="shared" ref="H32:H38" si="49">(F32+G32)/2</f>
+        <f t="shared" ref="H32:H38" si="55">(F32+G32)/2</f>
         <v>1.7320508100092411</v>
       </c>
       <c r="I32" s="3">
-        <f t="shared" ref="I32:I38" si="50">(F32)^2-3</f>
+        <f t="shared" ref="I32:I38" si="56">(F32)^2-3</f>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32:J38" si="51">(H32)^2-3</f>
+        <f t="shared" ref="J32:J38" si="57">(H32)^2-3</f>
         <v>8.4536684319402866E-9</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" ref="K32:K38" si="52">(I32)*(J32)</f>
+        <f t="shared" ref="K32:K38" si="58">(I32)*(J32)</f>
         <v>-3.7628258142260671E-17</v>
       </c>
       <c r="L32" s="2">
-        <f t="shared" ref="L32:L38" si="53">ABS((H32-F32)/H32)</f>
+        <f t="shared" ref="L32:L38" si="59">ABS((H32-F32)/H32)</f>
         <v>2.150797353596133E-9</v>
       </c>
       <c r="M32" s="2">
-        <f t="shared" ref="M32:M38" si="54">ABS(($C$7-H32)/$C$7)</f>
+        <f t="shared" ref="M32:M38" si="60">ABS(($C$7-H32)/$C$7)</f>
         <v>2.9336033049145562E-5</v>
       </c>
     </row>
@@ -5659,35 +6699,35 @@
         <v>28</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.7320508062839508</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.7320508100092411</v>
       </c>
       <c r="H33" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.732050808146596</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>2.0012760337806412E-9</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-8.9079116148554284E-18</v>
       </c>
       <c r="L33" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>1.0753986779545488E-9</v>
       </c>
       <c r="M33" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334957618920834E-5</v>
       </c>
     </row>
@@ -5696,35 +6736,35 @@
         <v>29</v>
       </c>
       <c r="F34" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.7320508062839508</v>
       </c>
       <c r="G34" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.732050808146596</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.7320508072152734</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-4.4511159202897943E-9</v>
       </c>
       <c r="J34" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>-1.2249197212099716E-9</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>5.4522596721546411E-18</v>
       </c>
       <c r="L34" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>5.3769933926639499E-10</v>
       </c>
       <c r="M34" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334419903808468E-5</v>
       </c>
     </row>
@@ -5733,35 +6773,35 @@
         <v>30</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.7320508072152734</v>
       </c>
       <c r="G35" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.732050808146596</v>
       </c>
       <c r="H35" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.7320508076809347</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-1.2249197212099716E-9</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>3.8817793424072988E-10</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-4.7548680699001754E-19</v>
       </c>
       <c r="L35" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>2.6884966956091732E-10</v>
       </c>
       <c r="M35" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334688761364651E-5</v>
       </c>
     </row>
@@ -5770,35 +6810,35 @@
         <v>31</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.7320508072152734</v>
       </c>
       <c r="G36" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.7320508076809347</v>
       </c>
       <c r="H36" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.732050807448104</v>
       </c>
       <c r="I36" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-1.2249197212099716E-9</v>
       </c>
       <c r="J36" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>-4.1837067144001594E-10</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>5.1247048622273296E-19</v>
       </c>
       <c r="L36" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>1.344248347985287E-10</v>
       </c>
       <c r="M36" s="2">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334554332586558E-5</v>
       </c>
     </row>
@@ -5807,35 +6847,35 @@
         <v>32</v>
       </c>
       <c r="F37" s="6">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.732050807448104</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.7320508076809347</v>
       </c>
       <c r="H37" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.7320508075645193</v>
       </c>
       <c r="I37" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-4.1837067144001594E-10</v>
       </c>
       <c r="J37" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>-1.5096368599643029E-11</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>6.315877867338627E-21</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>6.7212417394746847E-11</v>
       </c>
       <c r="M37" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334621546975604E-5</v>
       </c>
     </row>
@@ -5844,35 +6884,35 @@
         <v>33</v>
       </c>
       <c r="F38" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>1.7320508075645193</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>1.7320508076809347</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>1.732050807622727</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="56"/>
         <v>-1.5096368599643029E-11</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>1.8654100486514835E-10</v>
       </c>
       <c r="K38" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>-2.816091768392083E-21</v>
       </c>
       <c r="L38" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>3.3606208696244044E-11</v>
       </c>
       <c r="M38" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>2.9334655154170129E-5</v>
       </c>
     </row>
@@ -5899,6 +6939,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="AO4:AR4"/>
+    <mergeCell ref="AO5:AR5"/>
+    <mergeCell ref="AO6:AP6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="AD4:AG4"/>
+    <mergeCell ref="AD5:AG5"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="AD8:AE8"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="AD6:AG6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="O4:R4"/>
@@ -5911,17 +6962,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="AF8:AG8"/>
-    <mergeCell ref="AD6:AG6"/>
-    <mergeCell ref="AO4:AR4"/>
-    <mergeCell ref="AO5:AR5"/>
-    <mergeCell ref="AO6:AP6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="AD4:AG4"/>
-    <mergeCell ref="AD5:AG5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
